--- a/cl_st1_ph1_tatiana/examples/examples_summary.xlsx
+++ b/cl_st1_ph1_tatiana/examples/examples_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E481"/>
+  <dimension ref="A1:E561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12443,6 +12443,2006 @@
         <v>-8</v>
       </c>
     </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>f7_pos_001.tex</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>t010105</t>
+        </is>
+      </c>
+      <c r="E482" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>f7_pos_002.tex</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>t006615</t>
+        </is>
+      </c>
+      <c r="E483" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>f7_pos_003.tex</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>t008721</t>
+        </is>
+      </c>
+      <c r="E484" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>f7_pos_004.tex</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>t004806</t>
+        </is>
+      </c>
+      <c r="E485" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>f7_pos_005.tex</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>t005926</t>
+        </is>
+      </c>
+      <c r="E486" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>f7_pos_006.tex</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>t010553</t>
+        </is>
+      </c>
+      <c r="E487" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>f7_pos_007.tex</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>t010902</t>
+        </is>
+      </c>
+      <c r="E488" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>f7_pos_008.tex</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>t010941</t>
+        </is>
+      </c>
+      <c r="E489" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>f7_pos_009.tex</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>t010793</t>
+        </is>
+      </c>
+      <c r="E490" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>f7_pos_010.tex</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>t004539</t>
+        </is>
+      </c>
+      <c r="E491" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>f7_pos_011.tex</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>t002830</t>
+        </is>
+      </c>
+      <c r="E492" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>f7_pos_012.tex</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>t005286</t>
+        </is>
+      </c>
+      <c r="E493" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>f7_pos_013.tex</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>t009774</t>
+        </is>
+      </c>
+      <c r="E494" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>f7_pos_014.tex</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>t008957</t>
+        </is>
+      </c>
+      <c r="E495" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>f7_pos_015.tex</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>t001399</t>
+        </is>
+      </c>
+      <c r="E496" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>f7_pos_016.tex</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>t003642</t>
+        </is>
+      </c>
+      <c r="E497" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>f7_pos_017.tex</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>t010598</t>
+        </is>
+      </c>
+      <c r="E498" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>f7_pos_018.tex</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>t003694</t>
+        </is>
+      </c>
+      <c r="E499" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>f7_pos_019.tex</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>t007524</t>
+        </is>
+      </c>
+      <c r="E500" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>f7_pos_020.tex</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>t001161</t>
+        </is>
+      </c>
+      <c r="E501" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>f7_pos_021.tex</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>t009615</t>
+        </is>
+      </c>
+      <c r="E502" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>f7_pos_022.tex</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>t008924</t>
+        </is>
+      </c>
+      <c r="E503" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>f7_pos_023.tex</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>t013257</t>
+        </is>
+      </c>
+      <c r="E504" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>f7_pos_024.tex</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>t009429</t>
+        </is>
+      </c>
+      <c r="E505" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>f7_pos_025.tex</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>t010724</t>
+        </is>
+      </c>
+      <c r="E506" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>f7_pos_026.tex</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>t000263</t>
+        </is>
+      </c>
+      <c r="E507" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>f7_pos_027.tex</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>t007963</t>
+        </is>
+      </c>
+      <c r="E508" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>f7_pos_028.tex</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>t003019</t>
+        </is>
+      </c>
+      <c r="E509" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>f7_pos_029.tex</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>t003020</t>
+        </is>
+      </c>
+      <c r="E510" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>f7_pos_030.tex</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>t003021</t>
+        </is>
+      </c>
+      <c r="E511" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>f7_pos_031.tex</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>t008215</t>
+        </is>
+      </c>
+      <c r="E512" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>f7_pos_032.tex</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>t010562</t>
+        </is>
+      </c>
+      <c r="E513" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>f7_pos_033.tex</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>t002031</t>
+        </is>
+      </c>
+      <c r="E514" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>f7_pos_034.tex</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>t005258</t>
+        </is>
+      </c>
+      <c r="E515" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>f7_pos_035.tex</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>t011886</t>
+        </is>
+      </c>
+      <c r="E516" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>f7_pos_036.tex</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>t004512</t>
+        </is>
+      </c>
+      <c r="E517" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>f7_pos_037.tex</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>t011173</t>
+        </is>
+      </c>
+      <c r="E518" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>f7_pos_038.tex</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>t013886</t>
+        </is>
+      </c>
+      <c r="E519" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>f7_pos_039.tex</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>t003385</t>
+        </is>
+      </c>
+      <c r="E520" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>f7_pos_040.tex</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>t014407</t>
+        </is>
+      </c>
+      <c r="E521" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>f7_neg_001.tex</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>t012700</t>
+        </is>
+      </c>
+      <c r="E522" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>f7_neg_002.tex</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>t005320</t>
+        </is>
+      </c>
+      <c r="E523" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>f7_neg_003.tex</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>t014372</t>
+        </is>
+      </c>
+      <c r="E524" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>f7_neg_004.tex</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>t014416</t>
+        </is>
+      </c>
+      <c r="E525" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>f7_neg_005.tex</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>t014207</t>
+        </is>
+      </c>
+      <c r="E526" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>f7_neg_006.tex</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>t014160</t>
+        </is>
+      </c>
+      <c r="E527" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>f7_neg_007.tex</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>t014123</t>
+        </is>
+      </c>
+      <c r="E528" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>f7_neg_008.tex</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>t014388</t>
+        </is>
+      </c>
+      <c r="E529" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>f7_neg_009.tex</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>t013923</t>
+        </is>
+      </c>
+      <c r="E530" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>f7_neg_010.tex</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>t013917</t>
+        </is>
+      </c>
+      <c r="E531" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>f7_neg_011.tex</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>t013862</t>
+        </is>
+      </c>
+      <c r="E532" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>f7_neg_012.tex</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>t013834</t>
+        </is>
+      </c>
+      <c r="E533" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>f7_neg_013.tex</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>t013745</t>
+        </is>
+      </c>
+      <c r="E534" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>f7_neg_014.tex</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>t013640</t>
+        </is>
+      </c>
+      <c r="E535" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>f7_neg_015.tex</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>t013529</t>
+        </is>
+      </c>
+      <c r="E536" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>f7_neg_016.tex</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>t014348</t>
+        </is>
+      </c>
+      <c r="E537" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>f7_neg_017.tex</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>t013539</t>
+        </is>
+      </c>
+      <c r="E538" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>f7_neg_018.tex</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>t013459</t>
+        </is>
+      </c>
+      <c r="E539" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>f7_neg_019.tex</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>t013308</t>
+        </is>
+      </c>
+      <c r="E540" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>f7_neg_020.tex</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>t013438</t>
+        </is>
+      </c>
+      <c r="E541" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>f7_neg_021.tex</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>t013166</t>
+        </is>
+      </c>
+      <c r="E542" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>f7_neg_022.tex</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>t012968</t>
+        </is>
+      </c>
+      <c r="E543" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>f7_neg_023.tex</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>t012855</t>
+        </is>
+      </c>
+      <c r="E544" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>f7_neg_024.tex</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>t013259</t>
+        </is>
+      </c>
+      <c r="E545" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>f7_neg_025.tex</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>t012838</t>
+        </is>
+      </c>
+      <c r="E546" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>f7_neg_026.tex</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>t012818</t>
+        </is>
+      </c>
+      <c r="E547" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>f7_neg_027.tex</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>t012777</t>
+        </is>
+      </c>
+      <c r="E548" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>f7_neg_028.tex</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>t012452</t>
+        </is>
+      </c>
+      <c r="E549" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>f7_neg_029.tex</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>t012456</t>
+        </is>
+      </c>
+      <c r="E550" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>f7_neg_030.tex</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>t012416</t>
+        </is>
+      </c>
+      <c r="E551" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>f7_neg_031.tex</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>t012410</t>
+        </is>
+      </c>
+      <c r="E552" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>f7_neg_032.tex</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>t014069</t>
+        </is>
+      </c>
+      <c r="E553" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>f7_neg_033.tex</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>t012253</t>
+        </is>
+      </c>
+      <c r="E554" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>f7_neg_034.tex</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>t012228</t>
+        </is>
+      </c>
+      <c r="E555" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>f7_neg_035.tex</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>t012144</t>
+        </is>
+      </c>
+      <c r="E556" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>f7_neg_036.tex</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>t012145</t>
+        </is>
+      </c>
+      <c r="E557" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>f7_neg_037.tex</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>t012067</t>
+        </is>
+      </c>
+      <c r="E558" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>f7_neg_038.tex</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>t012068</t>
+        </is>
+      </c>
+      <c r="E559" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>f7_neg_039.tex</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>t012070</t>
+        </is>
+      </c>
+      <c r="E560" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>f7_neg_040.tex</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>fac7</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>t012016</t>
+        </is>
+      </c>
+      <c r="E561" t="n">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
